--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488147_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488147_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.302</v>
+        <v>2.8167</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3557</v>
+        <v>5.1166</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0537</v>
+        <v>-2.2999</v>
       </c>
       <c r="G2" t="n">
         <v>1.474</v>
@@ -610,13 +610,13 @@
         <v>0.9264</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0423</v>
+        <v>-0.5276</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0174</v>
+        <v>-0.2216</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0597</v>
+        <v>-0.3059</v>
       </c>
       <c r="V2" t="n">
         <v>0.9439</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6032</v>
+        <v>0.9036</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7612</v>
+        <v>-0.6086</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3644</v>
+        <v>1.5122</v>
       </c>
       <c r="G4" t="n">
         <v>1.3721</v>
@@ -766,13 +766,13 @@
         <v>1.297</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3291</v>
+        <v>-1.0287</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3071</v>
+        <v>-0.1545</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0219</v>
+        <v>-0.8742</v>
       </c>
       <c r="V4" t="n">
         <v>0.1897</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8893</v>
+        <v>-0.4277</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2256</v>
+        <v>0.5821</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1149</v>
+        <v>-1.0098</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.471</v>
+        <v>-0.0598</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1433</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6143</v>
+        <v>-0.7034</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6956</v>
+        <v>1.686</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3484</v>
+        <v>2.2974</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6529</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1665</v>
+        <v>-1.7458</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.2051</v>
+        <v>-1.6538</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0386</v>
+        <v>-0.092</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2892</v>
+        <v>-0.854</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0684</v>
+        <v>-0.1775</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3577</v>
+        <v>-0.6765</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3144</v>
+        <v>-0.4403</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6289</v>
+        <v>-0.4403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.088</v>
+        <v>-0.8643</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06950000000000001</v>
+        <v>-1.5958</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1575</v>
+        <v>0.7315</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0598</v>
+        <v>-2.8233</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6435999999999999</v>
+        <v>-2.2505</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7034</v>
+        <v>-0.5728</v>
       </c>
       <c r="J6" t="n">
-        <v>1.686</v>
+        <v>-1.591</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2974</v>
+        <v>-0.9796</v>
       </c>
       <c r="L6" t="n">
         <v>-0.6114000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7458</v>
+        <v>-1.2322</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6538</v>
+        <v>-1.2708</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.092</v>
+        <v>0.0386</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9264</v>
+        <v>2.2234</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8529</v>
+        <v>2.2234</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5144</v>
+        <v>-0.138</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6901</v>
+        <v>-0.0037</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8242</v>
+        <v>-0.1343</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4403</v>
+        <v>-0.1264</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.0011</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4403</v>
+        <v>-0.1253</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1624</v>
+        <v>-0.961</v>
       </c>
       <c r="E7" t="n">
-        <v>0.733</v>
+        <v>0.9836</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8954</v>
+        <v>-1.9446</v>
       </c>
       <c r="G7" t="n">
         <v>-1.906</v>
@@ -1000,13 +1000,13 @@
         <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4472</v>
+        <v>0.6485</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1219</v>
+        <v>0.1287</v>
       </c>
       <c r="U7" t="n">
-        <v>0.569</v>
+        <v>0.5198</v>
       </c>
       <c r="V7" t="n">
         <v>-0.63</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5487</v>
+        <v>-1.3319</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2064</v>
+        <v>-0.1432</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6577</v>
+        <v>-1.1888</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8233</v>
+        <v>-0.471</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2505</v>
+        <v>0.1433</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5728</v>
+        <v>-0.6143</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.591</v>
+        <v>1.6956</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9796</v>
+        <v>2.3484</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6529</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2322</v>
+        <v>-2.1665</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2708</v>
+        <v>-2.2051</v>
       </c>
       <c r="O8" t="n">
         <v>0.0386</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2234</v>
+        <v>0.1853</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2234</v>
+        <v>2.0382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8225</v>
+        <v>-0.7318</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6143</v>
+        <v>-0.3003</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2082</v>
+        <v>-0.4315</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1264</v>
+        <v>-0.3144</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0011</v>
+        <v>0.3144</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1253</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1462</v>
+        <v>-2.469</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.382</v>
+        <v>-0.1631</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7642</v>
+        <v>-2.3059</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8294</v>
@@ -1156,13 +1156,13 @@
         <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2532</v>
+        <v>-0.0696</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1803</v>
+        <v>0.0386</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4335</v>
+        <v>-0.1082</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7553</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7576</v>
+        <v>-2.629</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3517</v>
+        <v>-1.297</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4059</v>
+        <v>-1.332</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4036</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4096</v>
+        <v>-0.281</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1977</v>
+        <v>-0.143</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2119</v>
+        <v>-0.138</v>
       </c>
       <c r="V10" t="n">
         <v>-0.315</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6271</v>
+        <v>-3.1134</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0803</v>
+        <v>-3.7635</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4532</v>
+        <v>0.6502</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0058</v>
@@ -1312,13 +1312,13 @@
         <v>2.7793</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.254</v>
+        <v>-0.7402</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3991</v>
+        <v>-0.0824</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8548</v>
+        <v>-0.6579</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4409</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2152</v>
+        <v>-4.0855</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9002</v>
+        <v>-4.0413</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.315</v>
+        <v>-0.0442</v>
       </c>
       <c r="G12" t="n">
         <v>-4.8914</v>
@@ -1390,13 +1390,13 @@
         <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3243</v>
+        <v>-0.1946</v>
       </c>
       <c r="T12" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.0479</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4176</v>
+        <v>-0.1467</v>
       </c>
       <c r="V12" t="n">
         <v>0.63</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.5852</v>
+        <v>-11.2174</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3539</v>
+        <v>-3.9861</v>
       </c>
       <c r="F13" t="n">
         <v>-7.2313</v>
@@ -1447,7 +1447,7 @@
         <v>13.9704</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.372300000000001</v>
+        <v>-8.372299999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-17.1982</v>
@@ -1468,13 +1468,13 @@
         <v>15.7494</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.285</v>
+        <v>-3.917</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.331399999999999</v>
+        <v>-0.9636</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.9535</v>
+        <v>-2.9534</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2587</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2207</v>
+        <v>4.0417</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2509</v>
+        <v>1.1239</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9698</v>
+        <v>2.9178</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4585</v>
+        <v>1.2568</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0283</v>
+        <v>0.6918</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4301</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7137</v>
+        <v>1.1116</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5893</v>
+        <v>2.3746</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1244</v>
+        <v>-1.263</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2552</v>
+        <v>0.1452</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.561</v>
+        <v>-1.6828</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3057</v>
+        <v>1.828</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8529</v>
+        <v>-1.1117</v>
       </c>
       <c r="R14" t="n">
         <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2063</v>
+        <v>0.9696</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>0.4946</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5563</v>
+        <v>0.475</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2589</v>
+        <v>1.2594</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.26</v>
+        <v>0.6294</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0011</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2543</v>
+        <v>3.7284</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0688</v>
+        <v>1.2646</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1855</v>
+        <v>2.4638</v>
       </c>
       <c r="G15" t="n">
         <v>3.3214</v>
@@ -1624,13 +1624,13 @@
         <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3596</v>
+        <v>0.8338</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0037</v>
+        <v>0.1921</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3633</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.3144</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. DALLACOSTA ORTIZ</t>
+          <t>D. LARA CALDERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2125</v>
+        <v>3.2209</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0042</v>
+        <v>1.9468</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2083</v>
+        <v>1.2741</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4635</v>
+        <v>2.9842</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6958</v>
+        <v>-1.8298</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7677</v>
+        <v>4.8139</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7826</v>
+        <v>4.1126</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1901</v>
+        <v>0.7119</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5925</v>
+        <v>3.4006</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3191</v>
+        <v>-1.1284</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4943</v>
+        <v>-2.5417</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1751</v>
+        <v>1.4133</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.297</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8529</v>
+        <v>-4.8175</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>1.731</v>
+        <v>1.1845</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0744</v>
+        <v>0.4496</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6566</v>
+        <v>0.7349</v>
       </c>
       <c r="V16" t="n">
-        <v>0.315</v>
+        <v>2.2022</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.2022</v>
       </c>
       <c r="X16" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. LARA CALDERA</t>
+          <t>J. NDJUNGU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7072</v>
+        <v>3.0454</v>
       </c>
       <c r="E17" t="n">
-        <v>1.751</v>
+        <v>2.2696</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9563</v>
+        <v>0.7758</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9842</v>
+        <v>4.3749</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8298</v>
+        <v>0.8774</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8139</v>
+        <v>3.4975</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1126</v>
+        <v>5.3727</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7119</v>
+        <v>3.2885</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4006</v>
+        <v>2.0842</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1284</v>
+        <v>-0.9978</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.5417</v>
+        <v>-2.4111</v>
       </c>
       <c r="O17" t="n">
         <v>1.4133</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.1499</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.8175</v>
+        <v>-2.9646</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6708</v>
+        <v>0.7822</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2537</v>
+        <v>-0.138</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4171</v>
+        <v>0.9202</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2022</v>
+        <v>-0.6294</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2022</v>
+        <v>-0.0005</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NDJUNGU</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4343</v>
+        <v>3.037</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8779</v>
+        <v>0.8799</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5564</v>
+        <v>2.1571</v>
       </c>
       <c r="G18" t="n">
-        <v>4.3749</v>
+        <v>2.4585</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8774</v>
+        <v>1.0283</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4975</v>
+        <v>1.4301</v>
       </c>
       <c r="J18" t="n">
-        <v>5.3727</v>
+        <v>2.7137</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2885</v>
+        <v>2.5893</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0842</v>
+        <v>0.1244</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9978</v>
+        <v>-0.2552</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.4111</v>
+        <v>-1.561</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4133</v>
+        <v>1.3057</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4823</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9646</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1711</v>
+        <v>2.0226</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5296999999999999</v>
+        <v>1.279</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7008</v>
+        <v>0.7436</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6294</v>
+        <v>-1.2589</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0005</v>
+        <v>-1.26</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6289</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>L. DALLACOSTA ORTIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0814</v>
+        <v>2.6249</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1491</v>
+        <v>1.4166</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2306</v>
+        <v>1.2083</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2568</v>
+        <v>2.4635</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6918</v>
+        <v>0.6958</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.7677</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1116</v>
+        <v>2.7826</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3746</v>
+        <v>2.1901</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.263</v>
+        <v>0.5925</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1452</v>
+        <v>-0.3191</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6828</v>
+        <v>-1.4943</v>
       </c>
       <c r="O19" t="n">
-        <v>1.828</v>
+        <v>1.1751</v>
       </c>
       <c r="P19" t="n">
+        <v>-1.297</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.8529</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.5558999999999999</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.1117</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.6676</v>
-      </c>
       <c r="S19" t="n">
-        <v>-0.9906</v>
+        <v>1.1434</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7784</v>
+        <v>0.4869</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2122</v>
+        <v>0.6566</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2594</v>
+        <v>0.315</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.63</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0463</v>
+        <v>-0.0216</v>
       </c>
       <c r="E21" t="n">
         <v>0.0215</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0677</v>
+        <v>-0.0431</v>
       </c>
       <c r="G21" t="n">
         <v>-0.06270000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1515</v>
+        <v>-0.4505</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4375</v>
+        <v>1.0251</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.589</v>
+        <v>-1.4756</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9676</v>
@@ -2170,13 +2170,13 @@
         <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4989</v>
+        <v>0.2021</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4713</v>
+        <v>0.1163</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0276</v>
+        <v>0.0858</v>
       </c>
       <c r="V22" t="n">
         <v>0.315</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CANDELA SOLO DE ZALDIVAR</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.217</v>
+        <v>-2.3063</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8667</v>
+        <v>-1.4867</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3503</v>
+        <v>-0.8197</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1278</v>
+        <v>-2.4232</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-1.8303</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0292</v>
+        <v>-0.5929</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7683</v>
+        <v>-1.1584</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1074</v>
+        <v>-0.5884</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.8756</v>
+        <v>-0.5699</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3596</v>
+        <v>-1.2648</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.206</v>
+        <v>-1.2418</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1536</v>
+        <v>-0.023</v>
       </c>
       <c r="P23" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7991</v>
+        <v>-0.2537</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0869</v>
+        <v>-0.3283</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2878</v>
+        <v>0.0746</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>J. CANDELA SOLO DE ZALDIVAR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2325</v>
+        <v>-2.6981</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4867</v>
+        <v>-1.5522</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7458</v>
+        <v>-1.1459</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4232</v>
+        <v>-2.1278</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8303</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5929</v>
+        <v>-2.0292</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1584</v>
+        <v>-1.7683</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5884</v>
+        <v>0.1074</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5699</v>
+        <v>-1.8756</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2648</v>
+        <v>-0.3596</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2418</v>
+        <v>-0.206</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.023</v>
+        <v>-0.1536</v>
       </c>
       <c r="P24" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1798</v>
+        <v>0.318</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3283</v>
+        <v>0.4014</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1485</v>
+        <v>-0.0833</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>12.5852</v>
+        <v>14.54389999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>7.2314</v>
+        <v>7.2312</v>
       </c>
       <c r="F25" t="n">
-        <v>5.354100000000001</v>
+        <v>7.312600000000001</v>
       </c>
       <c r="G25" t="n">
         <v>11.6001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4644000000000001</v>
+        <v>0.4643999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>11.1356</v>
@@ -2383,7 +2383,7 @@
         <v>14.4349</v>
       </c>
       <c r="L25" t="n">
-        <v>2.763400000000001</v>
+        <v>2.7634</v>
       </c>
       <c r="M25" t="n">
         <v>-5.5982</v>
@@ -2395,7 +2395,7 @@
         <v>8.372199999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.558500000000001</v>
+        <v>-5.5585</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.7495</v>
@@ -2404,13 +2404,13 @@
         <v>10.1909</v>
       </c>
       <c r="S25" t="n">
-        <v>5.285000000000001</v>
+        <v>7.243499999999999</v>
       </c>
       <c r="T25" t="n">
         <v>2.9536</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3314</v>
+        <v>4.289999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>1.2588</v>
